--- a/products/store_b/out/02_Wedding_Guest_List_RSVP_Seating.xlsx
+++ b/products/store_b/out/02_Wedding_Guest_List_RSVP_Seating.xlsx
@@ -1129,11 +1129,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="15069678"/>
-        <c:axId val="38718436"/>
+        <c:axId val="33329173"/>
+        <c:axId val="77014940"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="15069678"/>
+        <c:axId val="33329173"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1165,7 +1165,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38718436"/>
+        <c:crossAx val="77014940"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1173,7 +1173,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38718436"/>
+        <c:axId val="77014940"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1215,7 +1215,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15069678"/>
+        <c:crossAx val="33329173"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1473,11 +1473,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="38733151"/>
-        <c:axId val="19430623"/>
+        <c:axId val="71328893"/>
+        <c:axId val="13639128"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38733151"/>
+        <c:axId val="71328893"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1509,7 +1509,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19430623"/>
+        <c:crossAx val="13639128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1517,7 +1517,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19430623"/>
+        <c:axId val="13639128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1559,7 +1559,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38733151"/>
+        <c:crossAx val="71328893"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
